--- a/XLibur.Tests/Resource/Examples/PageSetup/Sheets.xlsx
+++ b/XLibur.Tests/Resource/Examples/PageSetup/Sheets.xlsx
@@ -391,10 +391,10 @@
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:rowBreaks count="1" manualBreakCount="1">
-    <x:brk id="2" max="1048576" man="1"/>
+    <x:brk id="2" max="16383" man="1"/>
   </x:rowBreaks>
   <x:colBreaks count="1" manualBreakCount="1">
-    <x:brk id="2" max="16384" man="1"/>
+    <x:brk id="2" max="1048575" man="1"/>
   </x:colBreaks>
   <x:tableParts count="0"/>
 </x:worksheet>
